--- a/data/products_master_Hong_260513_K_Wellness_Spa 수정_v2.xlsx
+++ b/data/products_master_Hong_260513_K_Wellness_Spa 수정_v2.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3B22C8-FD32-4AF7-86B3-E5330835D08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7998B32B-6E2C-439E-B422-D7C76707AADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K-Medical" sheetId="1" r:id="rId1"/>
@@ -8511,7 +8511,9 @@
       <c r="J8" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="K8" s="10"/>
+      <c r="K8" s="10">
+        <v>1000000</v>
+      </c>
       <c r="L8" s="2" t="s">
         <v>31</v>
       </c>
